--- a/artfynd/A 25940-2025 artfynd.xlsx
+++ b/artfynd/A 25940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>117125515</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117125510</v>
+        <v>117125518</v>
       </c>
       <c r="B3" t="n">
-        <v>78444</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607350</v>
+        <v>607246</v>
       </c>
       <c r="R3" t="n">
-        <v>6959703</v>
+        <v>6959600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,16 +872,11 @@
         <v>117125517</v>
       </c>
       <c r="B4" t="n">
-        <v>90905</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,12 +889,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117125518</v>
+        <v>117125520</v>
       </c>
       <c r="B5" t="n">
-        <v>90463</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607246</v>
+        <v>607114</v>
       </c>
       <c r="R5" t="n">
-        <v>6959600</v>
+        <v>6959598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,6 +1060,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117125510</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-Långmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>607350</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6959703</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25940-2025 artfynd.xlsx
+++ b/artfynd/A 25940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125515</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125517</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117125510</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>